--- a/diseases/d128/2000-2004.xlsx
+++ b/diseases/d128/2000-2004.xlsx
@@ -6197,12 +6197,12 @@
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -6227,53 +6227,64 @@
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>2003-02-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>2003-02</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N39" t="n">
-        <v>2</v>
+        <v>1488</v>
       </c>
       <c r="O39" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q39" t="n">
-        <v>0</v>
+        <v>1488</v>
       </c>
       <c r="R39" t="n">
-        <v>0.01009109509043248</v>
+        <v>4.673883251296422</v>
       </c>
       <c r="S39" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP39" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR39" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS39" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ39" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS39" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT39" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU39" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV39" t="inlineStr">
@@ -6283,17 +6294,17 @@
       </c>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ39" t="inlineStr">
@@ -6303,17 +6314,17 @@
       </c>
       <c r="BA39" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB39" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC39" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6340,17 +6351,17 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -6375,53 +6386,139 @@
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>2003-03-01</t>
+          <t>2003-01-01</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>2003-03</t>
+          <t>2003-01</t>
         </is>
       </c>
       <c r="N40" t="n">
-        <v>3</v>
+        <v>1488</v>
       </c>
       <c r="O40" t="n">
-        <v>3</v>
-      </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
-      <c r="R40" t="n">
-        <v>0.01513664263564873</v>
-      </c>
-      <c r="S40" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1488</v>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X40" t="inlineStr">
+        <is>
+          <t>West Nile Virus Infection</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD40" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE40" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF40" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG40" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH40" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ40" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK40" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM40" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN40" t="b">
+        <v>1</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP40" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR40" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS40" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ40" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS40" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU40" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV40" t="inlineStr">
@@ -6431,17 +6528,17 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
@@ -6451,17 +6548,17 @@
       </c>
       <c r="BA40" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB40" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC40" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -6523,25 +6620,25 @@
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>2003-04-01</t>
+          <t>2003-02-01</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>2003-04</t>
+          <t>2003-02</t>
         </is>
       </c>
       <c r="N41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Q41" t="n">
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0.005045547545216242</v>
+        <v>0.01009109509043248</v>
       </c>
       <c r="S41" t="inlineStr">
         <is>
@@ -6671,25 +6768,25 @@
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>2003-05-01</t>
+          <t>2003-03-01</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>2003-05</t>
+          <t>2003-03</t>
         </is>
       </c>
       <c r="N42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O42" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q42" t="n">
         <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>0.01513664263564873</v>
       </c>
       <c r="S42" t="inlineStr">
         <is>
@@ -6819,25 +6916,25 @@
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>2003-06-01</t>
+          <t>2003-04-01</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>2003-06</t>
+          <t>2003-04</t>
         </is>
       </c>
       <c r="N43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O43" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q43" t="n">
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>0.005045547545216242</v>
       </c>
       <c r="S43" t="inlineStr">
         <is>
@@ -6967,12 +7064,12 @@
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>2003-07-01</t>
+          <t>2003-05-01</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>2003-07</t>
+          <t>2003-05</t>
         </is>
       </c>
       <c r="N44" t="n">
@@ -7115,12 +7212,12 @@
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>2003-08-01</t>
+          <t>2003-06-01</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>2003-08</t>
+          <t>2003-06</t>
         </is>
       </c>
       <c r="N45" t="n">
@@ -7263,25 +7360,25 @@
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>2003-09-01</t>
+          <t>2003-07-01</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>2003-09</t>
+          <t>2003-07</t>
         </is>
       </c>
       <c r="N46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O46" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
         <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.005045547545216242</v>
+        <v>0</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7411,25 +7508,25 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2003-10-01</t>
+          <t>2003-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>2003-10</t>
+          <t>2003-08</t>
         </is>
       </c>
       <c r="N47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O47" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
         <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>0.005045547545216242</v>
+        <v>0</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7559,12 +7656,12 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2003-11-01</t>
+          <t>2003-09-01</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>2003-11</t>
+          <t>2003-09</t>
         </is>
       </c>
       <c r="N48" t="n">
@@ -7707,25 +7804,25 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2003-12-01</t>
+          <t>2003-10-01</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>2003-12</t>
+          <t>2003-10</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q49" t="n">
         <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>0.005045547545216242</v>
       </c>
       <c r="S49" t="inlineStr">
         <is>
@@ -7855,12 +7952,12 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2004-01-01</t>
+          <t>2003-11-01</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>2004-01</t>
+          <t>2003-11</t>
         </is>
       </c>
       <c r="N50" t="n">
@@ -7873,7 +7970,7 @@
         <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>0.004988357920866386</v>
+        <v>0.005045547545216242</v>
       </c>
       <c r="S50" t="inlineStr">
         <is>
@@ -8003,25 +8100,25 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2004-02-01</t>
+          <t>2003-12-01</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2004-02</t>
+          <t>2003-12</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O51" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
         <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>0.01496507376259916</v>
+        <v>0</v>
       </c>
       <c r="S51" t="inlineStr">
         <is>
@@ -8151,25 +8248,25 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2004-03-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2004-03</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52" t="n">
         <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>0.004988357920866386</v>
       </c>
       <c r="S52" t="inlineStr">
         <is>
@@ -8269,12 +8366,12 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
@@ -8299,53 +8396,64 @@
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>2004-04-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>2004-04</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q53" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.09958709478847508</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP53" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR53" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS53" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ53" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU53" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV53" t="inlineStr">
@@ -8355,17 +8463,17 @@
       </c>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ53" t="inlineStr">
@@ -8375,17 +8483,17 @@
       </c>
       <c r="BA53" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB53" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC53" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8412,17 +8520,17 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>CA</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -8447,53 +8555,139 @@
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>2004-05-01</t>
+          <t>2004-01-01</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>2004-05</t>
+          <t>2004-01</t>
         </is>
       </c>
       <c r="N54" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="O54" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>0</v>
-      </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>32</v>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>SRC_CA_PHAC_CNDSS</t>
+        </is>
+      </c>
+      <c r="X54" t="inlineStr">
+        <is>
+          <t>West Nile Virus Infection</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>provincial_territorial_voluntary_notifications_national</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>annual</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>country:CA:national</t>
+        </is>
+      </c>
+      <c r="AD54" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE54" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF54" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG54" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH54" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI54" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ54" t="inlineStr">
+        <is>
+          <t>CNDSS_NATIONAL_ANNUAL_2026_08</t>
+        </is>
+      </c>
+      <c r="AK54" t="inlineStr">
+        <is>
+          <t>PHAC CNDSS national annual reported count assembled from voluntary provincial and territorial submissions. Disease-specific reporting coverage and definitions vary over time; null cells are unknown and explicit zeroes are retained.</t>
+        </is>
+      </c>
+      <c r="AM54" t="inlineStr">
+        <is>
+          <t>raw</t>
+        </is>
+      </c>
+      <c r="AN54" t="b">
+        <v>1</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP54" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR54" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS54" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ54" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr">
+        <is>
+          <t>SER_CA_PHAC_CNDSS_D196_ANNUAL</t>
+        </is>
+      </c>
       <c r="AT54" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU54" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV54" t="inlineStr">
@@ -8503,17 +8697,17 @@
       </c>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ54" t="inlineStr">
@@ -8523,17 +8717,17 @@
       </c>
       <c r="BA54" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Canada PHAC CNDSS Annual</t>
         </is>
       </c>
       <c r="BB54" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://diseases.canada.ca/notifiable/extract-dataset</t>
         </is>
       </c>
       <c r="BC54" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8595,25 +8789,25 @@
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>2004-06-01</t>
+          <t>2004-02-01</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>2004-06</t>
+          <t>2004-02</t>
         </is>
       </c>
       <c r="N55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O55" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q55" t="n">
         <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>0.01496507376259916</v>
       </c>
       <c r="S55" t="inlineStr">
         <is>
@@ -8743,12 +8937,12 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>2004-07-01</t>
+          <t>2004-03-01</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>2004-07</t>
+          <t>2004-03</t>
         </is>
       </c>
       <c r="N56" t="n">
@@ -8891,12 +9085,12 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2004-08-01</t>
+          <t>2004-04-01</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2004-08</t>
+          <t>2004-04</t>
         </is>
       </c>
       <c r="N57" t="n">
@@ -9039,12 +9233,12 @@
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>2004-09-01</t>
+          <t>2004-05-01</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>2004-09</t>
+          <t>2004-05</t>
         </is>
       </c>
       <c r="N58" t="n">
@@ -9187,25 +9381,25 @@
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>2004-10-01</t>
+          <t>2004-06-01</t>
         </is>
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>2004-10</t>
+          <t>2004-06</t>
         </is>
       </c>
       <c r="N59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O59" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
         <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>0.004988357920866386</v>
+        <v>0</v>
       </c>
       <c r="S59" t="inlineStr">
         <is>
@@ -9335,12 +9529,12 @@
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>2004-11-01</t>
+          <t>2004-07-01</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>2004-11</t>
+          <t>2004-07</t>
         </is>
       </c>
       <c r="N60" t="n">
@@ -9483,25 +9677,25 @@
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>2004-12-01</t>
+          <t>2004-08-01</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>2004-12</t>
+          <t>2004-08</t>
         </is>
       </c>
       <c r="N61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O61" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
         <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>0.004988357920866386</v>
+        <v>0</v>
       </c>
       <c r="S61" t="inlineStr">
         <is>
@@ -9568,6 +9762,598 @@
         </is>
       </c>
       <c r="BC61" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>2004-09-01</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>2004-09</t>
+        </is>
+      </c>
+      <c r="N62" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q62" t="n">
+        <v>0</v>
+      </c>
+      <c r="R62" t="n">
+        <v>0</v>
+      </c>
+      <c r="S62" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP62" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR62" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS62" t="inlineStr"/>
+      <c r="AT62" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU62" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA62" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB62" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC62" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>2004-10-01</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>2004-10</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>0</v>
+      </c>
+      <c r="R63" t="n">
+        <v>0.004988357920866386</v>
+      </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP63" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR63" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS63" t="inlineStr"/>
+      <c r="AT63" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU63" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA63" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB63" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC63" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>2004-11-01</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>2004-11</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q64" t="n">
+        <v>0</v>
+      </c>
+      <c r="R64" t="n">
+        <v>0</v>
+      </c>
+      <c r="S64" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP64" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR64" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS64" t="inlineStr"/>
+      <c r="AT64" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU64" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA64" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB64" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC64" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>west-nile-virus</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>D128</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>West Nile virus</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>西尼罗病毒</t>
+        </is>
+      </c>
+      <c r="K65" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>2004-12-01</t>
+        </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>2004-12</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>1</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0.004988357920866386</v>
+      </c>
+      <c r="S65" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP65" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR65" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS65" t="inlineStr"/>
+      <c r="AT65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU65" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr">
+        <is>
+          <t>microsoft_bi</t>
+        </is>
+      </c>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="BA65" t="inlineStr">
+        <is>
+          <t>Australia NINDSS</t>
+        </is>
+      </c>
+      <c r="BB65" t="inlineStr">
+        <is>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+        </is>
+      </c>
+      <c r="BC65" t="inlineStr">
         <is>
           <t>microsoft_bi</t>
         </is>
@@ -9689,7 +10475,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10">
@@ -9699,7 +10485,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11">
@@ -9719,7 +10505,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -9729,7 +10515,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -9751,7 +10537,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>1539</v>
       </c>
     </row>
     <row r="16">
